--- a/output/pdf_financials_xlsx/DHB.xlsx
+++ b/output/pdf_financials_xlsx/DHB.xlsx
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005814</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.02497</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -2678,25 +2678,25 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>20.301</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>4.431</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.084</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.721</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>3.302</v>
       </c>
     </row>
     <row r="35">
@@ -2804,25 +2804,25 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>20.301</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.711</v>
+        <v>5.142</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.026</v>
+        <v>1.11</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.011</v>
+        <v>2.732</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>3.302</v>
       </c>
     </row>
     <row r="37">
@@ -3560,25 +3560,25 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>23.025</v>
+        <v>2.724</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>17.454</v>
+        <v>16.048</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.825</v>
+        <v>0.394</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.663</v>
+        <v>2.579</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.058</v>
+        <v>0.337</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.331</v>
+        <v>0.131</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3.479</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="49">
@@ -8430,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-4.082</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.309</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.255</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.225</v>
       </c>
       <c r="S124" s="3" t="n">
         <v>0</v>
@@ -8491,16 +8491,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-4.082</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.309</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.255</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.225</v>
       </c>
       <c r="S125" s="3" t="n">
         <v>0</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -26644,7 +26644,11 @@
           <t>Repayment of loans and lease payments 9</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -44960,7 +44964,11 @@
           <t>Repayment of loans and lease payments 10</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -58992,7 +59000,11 @@
           <t>Repayment of loans and lease payments 11</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -85544,7 +85556,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E729" t="inlineStr">
